--- a/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PARA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>PARA</t>
   </si>
@@ -656,172 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I7" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="I7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>29213000</v>
+        <v>12200</v>
       </c>
       <c r="E8" s="3">
-        <v>29652000</v>
+        <v>4500</v>
       </c>
       <c r="F8" s="3">
-        <v>30154000</v>
+        <v>4600</v>
       </c>
       <c r="G8" s="3">
-        <v>28586000</v>
+        <v>5300</v>
       </c>
       <c r="H8" s="3">
-        <v>25285000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>26998000</v>
-      </c>
-      <c r="J8" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>26425000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26535000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13166000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12671000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19437000</v>
+        <v>2200</v>
       </c>
       <c r="E9" s="3">
-        <v>20017000</v>
+        <v>1400</v>
       </c>
       <c r="F9" s="3">
-        <v>19845000</v>
+        <v>1400</v>
       </c>
       <c r="G9" s="3">
-        <v>17744000</v>
+        <v>2000</v>
       </c>
       <c r="H9" s="3">
-        <v>14833000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>16124000</v>
-      </c>
-      <c r="J9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>15399000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15483000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7956000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7911000</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9776000</v>
+        <v>10000</v>
       </c>
       <c r="E10" s="3">
-        <v>9635000</v>
+        <v>3100</v>
       </c>
       <c r="F10" s="3">
-        <v>10309000</v>
+        <v>3100</v>
       </c>
       <c r="G10" s="3">
-        <v>10842000</v>
+        <v>3400</v>
       </c>
       <c r="H10" s="3">
-        <v>10452000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>10874000</v>
-      </c>
-      <c r="J10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>11026000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11052000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5210000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4760000</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,16 +850,17 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1000</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -871,9 +886,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +925,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7950000</v>
+        <v>3200</v>
       </c>
       <c r="E14" s="3">
-        <v>2262000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>685000</v>
+        <v>14500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>-2162000</v>
+        <v>2100</v>
       </c>
       <c r="H14" s="3">
-        <v>515000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>744000</v>
-      </c>
-      <c r="J14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>524000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>235000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>249000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>390000</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>392000</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>378000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>390000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>393000</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>418000</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>427000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>443000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>225000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>235000</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1020,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26688000</v>
+        <v>30600</v>
       </c>
       <c r="E17" s="3">
-        <v>27797000</v>
+        <v>18000</v>
       </c>
       <c r="F17" s="3">
-        <v>27321000</v>
+        <v>14400</v>
       </c>
       <c r="G17" s="3">
-        <v>24585000</v>
+        <v>11200</v>
       </c>
       <c r="H17" s="3">
-        <v>20620000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>22122000</v>
-      </c>
-      <c r="J17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>20939000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21178000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10475000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10013000</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2525000</v>
+        <v>-18500</v>
       </c>
       <c r="E18" s="3">
-        <v>1855000</v>
+        <v>-13500</v>
       </c>
       <c r="F18" s="3">
-        <v>2833000</v>
+        <v>-9800</v>
       </c>
       <c r="G18" s="3">
-        <v>4001000</v>
+        <v>-5900</v>
       </c>
       <c r="H18" s="3">
-        <v>4665000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4876000</v>
-      </c>
-      <c r="J18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>5486000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5357000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2691000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2658000</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,188 +1115,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>334000</v>
+        <v>-2300</v>
       </c>
       <c r="E20" s="3">
-        <v>423000</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>263000</v>
+        <v>-900</v>
       </c>
       <c r="G20" s="3">
-        <v>115000</v>
+        <v>5100</v>
       </c>
       <c r="H20" s="3">
-        <v>60000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>66000</v>
-      </c>
-      <c r="J20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>74000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-50000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5000</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2583000</v>
+        <v>-15000</v>
       </c>
       <c r="E21" s="3">
-        <v>1850000</v>
+        <v>-13300</v>
       </c>
       <c r="F21" s="3">
-        <v>2948000</v>
+        <v>-8800</v>
       </c>
       <c r="G21" s="3">
-        <v>4276000</v>
+        <v>-11000</v>
       </c>
       <c r="H21" s="3">
-        <v>4998000</v>
+        <v>-7100</v>
       </c>
       <c r="I21" s="3">
-        <v>5228000</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>5839000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5803000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2866000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2898000</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>860000</v>
+        <v>2400</v>
       </c>
       <c r="E22" s="3">
-        <v>920000</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="3">
-        <v>931000</v>
+        <v>5600</v>
       </c>
       <c r="G22" s="3">
-        <v>986000</v>
+        <v>2400</v>
       </c>
       <c r="H22" s="3">
-        <v>1031000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>962000</v>
-      </c>
-      <c r="J22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>1030000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1088000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>411000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>399000</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6468000</v>
+        <v>-22400</v>
       </c>
       <c r="E23" s="3">
-        <v>-1613000</v>
+        <v>-31500</v>
       </c>
       <c r="F23" s="3">
-        <v>1062000</v>
+        <v>-14400</v>
       </c>
       <c r="G23" s="3">
-        <v>5115000</v>
+        <v>-15500</v>
       </c>
       <c r="H23" s="3">
-        <v>3119000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>3170000</v>
-      </c>
-      <c r="J23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>3937000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4124000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2230000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2264000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-305000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-361000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>227000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>646000</v>
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
-        <v>535000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-29000</v>
-      </c>
-      <c r="J24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>580000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>804000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>628000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>676000</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1346,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6163000</v>
+        <v>-22500</v>
       </c>
       <c r="E26" s="3">
-        <v>-1252000</v>
+        <v>-31500</v>
       </c>
       <c r="F26" s="3">
-        <v>835000</v>
+        <v>-14400</v>
       </c>
       <c r="G26" s="3">
-        <v>4469000</v>
+        <v>-15500</v>
       </c>
       <c r="H26" s="3">
-        <v>2584000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>3199000</v>
-      </c>
-      <c r="J26" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>3357000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3320000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1602000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1588000</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6204000</v>
+        <v>-22500</v>
       </c>
       <c r="E27" s="3">
-        <v>-666000</v>
+        <v>-31100</v>
       </c>
       <c r="F27" s="3">
-        <v>1046000</v>
+        <v>-14400</v>
       </c>
       <c r="G27" s="3">
-        <v>4499000</v>
+        <v>-15500</v>
       </c>
       <c r="H27" s="3">
-        <v>2422000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3308000</v>
-      </c>
-      <c r="J27" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>3455000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2321000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1552000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1554000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,45 +1463,51 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>676000</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>379000</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>162000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>135000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-947000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-291000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-141000</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1580,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-334000</v>
+        <v>2300</v>
       </c>
       <c r="E32" s="3">
-        <v>-423000</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-263000</v>
+        <v>900</v>
       </c>
       <c r="G32" s="3">
-        <v>-115000</v>
+        <v>-5100</v>
       </c>
       <c r="H32" s="3">
-        <v>-60000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-66000</v>
-      </c>
-      <c r="J32" s="3">
+        <v>800</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-74000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>50000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5000</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6190000</v>
+        <v>-22500</v>
       </c>
       <c r="E33" s="3">
-        <v>-608000</v>
+        <v>-31500</v>
       </c>
       <c r="F33" s="3">
-        <v>1104000</v>
+        <v>-14400</v>
       </c>
       <c r="G33" s="3">
-        <v>4543000</v>
+        <v>-15500</v>
       </c>
       <c r="H33" s="3">
-        <v>2422000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3308000</v>
-      </c>
-      <c r="J33" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>3455000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2321000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1261000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1413000</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1697,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6190000</v>
+        <v>-22500</v>
       </c>
       <c r="E35" s="3">
-        <v>-608000</v>
+        <v>-31500</v>
       </c>
       <c r="F35" s="3">
-        <v>1104000</v>
+        <v>-14400</v>
       </c>
       <c r="G35" s="3">
-        <v>4543000</v>
+        <v>-15500</v>
       </c>
       <c r="H35" s="3">
-        <v>2422000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>3308000</v>
-      </c>
-      <c r="J35" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>3455000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2321000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1261000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1413000</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I38" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="I38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,44 +1817,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2661000</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
-        <v>2460000</v>
+        <v>1100</v>
       </c>
       <c r="F41" s="3">
-        <v>2885000</v>
+        <v>2100</v>
       </c>
       <c r="G41" s="3">
-        <v>6267000</v>
+        <v>1000</v>
       </c>
       <c r="H41" s="3">
-        <v>2984000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>632000</v>
-      </c>
-      <c r="J41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>856000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>285000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>598000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>323000</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1801,261 +1892,285 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6920000</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
-        <v>7115000</v>
+        <v>900</v>
       </c>
       <c r="F43" s="3">
-        <v>7412000</v>
+        <v>100</v>
       </c>
       <c r="G43" s="3">
-        <v>6984000</v>
+        <v>100</v>
       </c>
       <c r="H43" s="3">
-        <v>7017000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>6837000</v>
-      </c>
-      <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>7199000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3697000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3314000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3628000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>1429000</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1414000</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1342000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1504000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1757000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>2813000</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>2785000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1828000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1427000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1271000</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>37000</v>
+        <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>787000</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
-        <v>745000</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>630000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1221000</v>
-      </c>
-      <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>668000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>269000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>724000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>525000</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12542000</v>
+        <v>1400</v>
       </c>
       <c r="E46" s="3">
-        <v>12703000</v>
+        <v>2700</v>
       </c>
       <c r="F46" s="3">
-        <v>13734000</v>
+        <v>2900</v>
       </c>
       <c r="G46" s="3">
-        <v>16676000</v>
+        <v>1400</v>
       </c>
       <c r="H46" s="3">
-        <v>13779000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>11902000</v>
-      </c>
-      <c r="J46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>11880000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6273000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6063000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5747000</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>185000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>708000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>375000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>568000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>601000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>753000</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>719000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>307000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2578000</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>2849000</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>3153000</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>3366000</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
-        <v>3596000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3783000</v>
-      </c>
-      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>2079000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1246000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1241000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1405000</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>12914000</v>
+        <v>30000</v>
       </c>
       <c r="E49" s="3">
-        <v>19105000</v>
+        <v>22900</v>
       </c>
       <c r="F49" s="3">
-        <v>19193000</v>
+        <v>2200</v>
       </c>
       <c r="G49" s="3">
-        <v>19356000</v>
+        <v>2200</v>
       </c>
       <c r="H49" s="3">
-        <v>19438000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>19535000</v>
-      </c>
-      <c r="J49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" s="3">
         <v>19469000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7557000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7497000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11995000</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2243,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16567000</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>16936000</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>20696000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>17448000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>14256000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>12674000</v>
-      </c>
-      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>10084000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5449000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9437000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4618000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>46172000</v>
+        <v>31600</v>
       </c>
       <c r="E54" s="3">
-        <v>53543000</v>
+        <v>25700</v>
       </c>
       <c r="F54" s="3">
-        <v>58393000</v>
+        <v>5300</v>
       </c>
       <c r="G54" s="3">
-        <v>58620000</v>
+        <v>5500</v>
       </c>
       <c r="H54" s="3">
-        <v>52663000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>49585000</v>
-      </c>
-      <c r="J54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>44497000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20843000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24238000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23765000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,224 +2397,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>953000</v>
+        <v>2500</v>
       </c>
       <c r="E57" s="3">
-        <v>1100000</v>
+        <v>7800</v>
       </c>
       <c r="F57" s="3">
-        <v>1403000</v>
+        <v>6400</v>
       </c>
       <c r="G57" s="3">
-        <v>800000</v>
+        <v>1100</v>
       </c>
       <c r="H57" s="3">
-        <v>571000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>632000</v>
-      </c>
-      <c r="J57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>502000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>231000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>148000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>192000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>284000</v>
+        <v>10600</v>
       </c>
       <c r="E58" s="3">
-        <v>259000</v>
+        <v>12500</v>
       </c>
       <c r="F58" s="3">
-        <v>531000</v>
+        <v>16500</v>
       </c>
       <c r="G58" s="3">
-        <v>336000</v>
+        <v>14000</v>
       </c>
       <c r="H58" s="3">
-        <v>322000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1006000</v>
-      </c>
-      <c r="J58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>1013000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>698000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>473000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>222000</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6195000</v>
+        <v>5700</v>
       </c>
       <c r="E59" s="3">
-        <v>6193000</v>
+        <v>4300</v>
       </c>
       <c r="F59" s="3">
-        <v>7186000</v>
+        <v>9200</v>
       </c>
       <c r="G59" s="3">
-        <v>6020000</v>
+        <v>13500</v>
       </c>
       <c r="H59" s="3">
-        <v>5689000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>5681000</v>
-      </c>
-      <c r="J59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>5173000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2246000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3087000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3146000</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9631000</v>
+        <v>22400</v>
       </c>
       <c r="E60" s="3">
-        <v>9656000</v>
+        <v>28300</v>
       </c>
       <c r="F60" s="3">
-        <v>11191000</v>
+        <v>37100</v>
       </c>
       <c r="G60" s="3">
-        <v>9479000</v>
+        <v>29300</v>
       </c>
       <c r="H60" s="3">
-        <v>8296000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>9048000</v>
-      </c>
-      <c r="J60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>8321000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3972000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3708000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3560000</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15549000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>15857000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>17035000</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>19296000</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>21300000</v>
+        <v>3400</v>
       </c>
       <c r="I61" s="3">
-        <v>19707000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>18100000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9464000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8902000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8226000</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2875000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3086000</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
-        <v>3939000</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
-        <v>3650000</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>3796000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>4430000</v>
-      </c>
-      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>4668000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3621000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5488000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6344000</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29390000</v>
+        <v>23600</v>
       </c>
       <c r="E66" s="3">
-        <v>30493000</v>
+        <v>28400</v>
       </c>
       <c r="F66" s="3">
-        <v>34787000</v>
+        <v>37200</v>
       </c>
       <c r="G66" s="3">
-        <v>35543000</v>
+        <v>29600</v>
       </c>
       <c r="H66" s="3">
-        <v>36410000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>36042000</v>
-      </c>
-      <c r="J66" s="3">
+        <v>14300</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>33755000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18865000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20549000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18202000</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2732,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -2749,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2957,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7487000</v>
+        <v>-100800</v>
       </c>
       <c r="E72" s="3">
-        <v>13829000</v>
+        <v>-78300</v>
       </c>
       <c r="F72" s="3">
-        <v>14737000</v>
+        <v>-46800</v>
       </c>
       <c r="G72" s="3">
-        <v>14343000</v>
+        <v>-32400</v>
       </c>
       <c r="H72" s="3">
-        <v>10375000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>8494000</v>
-      </c>
-      <c r="J72" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>5569000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-18900000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-19257000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20518000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16320000</v>
+        <v>8100</v>
       </c>
       <c r="E76" s="3">
-        <v>22526000</v>
+        <v>-2800</v>
       </c>
       <c r="F76" s="3">
-        <v>23036000</v>
+        <v>-31900</v>
       </c>
       <c r="G76" s="3">
-        <v>22402000</v>
+        <v>-24100</v>
       </c>
       <c r="H76" s="3">
-        <v>15371000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>13207000</v>
-      </c>
-      <c r="J76" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>10449000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1978000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3689000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5563000</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3191,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
-        <v>44196</v>
-      </c>
-      <c r="I80" s="2">
-        <v>43830</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="I80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6190000</v>
+        <v>-22500</v>
       </c>
       <c r="E81" s="3">
-        <v>-608000</v>
+        <v>-31500</v>
       </c>
       <c r="F81" s="3">
-        <v>1104000</v>
+        <v>-14400</v>
       </c>
       <c r="G81" s="3">
-        <v>4543000</v>
+        <v>-15500</v>
       </c>
       <c r="H81" s="3">
-        <v>2422000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>3308000</v>
-      </c>
-      <c r="J81" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>3455000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2321000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1261000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1413000</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3294,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>364000</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>383000</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>337000</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>344000</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>333000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>362000</v>
-      </c>
-      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>377000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>395000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>225000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>235000</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3525,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>752000</v>
+        <v>-15700</v>
       </c>
       <c r="E89" s="3">
-        <v>475000</v>
+        <v>-9600</v>
       </c>
       <c r="F89" s="3">
-        <v>219000</v>
+        <v>-1600</v>
       </c>
       <c r="G89" s="3">
-        <v>953000</v>
+        <v>-5200</v>
       </c>
       <c r="H89" s="3">
-        <v>2294000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1230000</v>
-      </c>
-      <c r="J89" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>3464000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2439000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1685000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1394000</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3584,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-263000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-328000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-358000</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
-        <v>-354000</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-324000</v>
-      </c>
-      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-345000</v>
       </c>
-      <c r="J91" s="3">
-        <v>-345000</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-356000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-196000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-171000</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3698,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>12000</v>
+        <v>-2700</v>
       </c>
       <c r="E94" s="3">
-        <v>942000</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-526000</v>
+        <v>100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3">
-        <v>2395000</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>56000</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-155000</v>
-      </c>
-      <c r="J94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-611000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>126000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-340000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>154000</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,44 +3757,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>389000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>631000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>617000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>595000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>599000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>616000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-288000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-300000</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3910,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-507000</v>
+        <v>17600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1841000</v>
+        <v>8500</v>
       </c>
       <c r="F100" s="3">
-        <v>-2981000</v>
+        <v>2600</v>
       </c>
       <c r="G100" s="3">
-        <v>-152000</v>
+        <v>4400</v>
       </c>
       <c r="H100" s="3">
-        <v>-90000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1216000</v>
-      </c>
-      <c r="J100" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2531000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3009000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1653000</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-94000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-48000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>25000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-25000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>58000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>201000</v>
+        <v>-800</v>
       </c>
       <c r="E102" s="3">
-        <v>-425000</v>
+        <v>-1000</v>
       </c>
       <c r="F102" s="3">
-        <v>-3382000</v>
+        <v>1100</v>
       </c>
       <c r="G102" s="3">
-        <v>3148000</v>
+        <v>-800</v>
       </c>
       <c r="H102" s="3">
-        <v>2285000</v>
+        <v>1000</v>
       </c>
       <c r="I102" s="3">
-        <v>-142000</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>297000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-386000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>299000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-105000</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
